--- a/entregables/gestion-proyectos/bases/Base_General.xlsx
+++ b/entregables/gestion-proyectos/bases/Base_General.xlsx
@@ -622,14 +622,14 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Abra la aplicación → módulo 09 Bases y auditoría → tarjeta «Bases de alimentación (Excel)» →</t>
+          <t>Abra la aplicación → barra lateral → Bases y auditoría → «Cargar base de alimentación (Excel)» →</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>«Subir base de alimentación» → elija este archivo. La carga NO borra lo existente: crea lo nuevo y</t>
+          <t>elija este archivo (también desde la pestaña Guía, botón «Cargar una base ahora»). La carga NO borra lo existente: crea lo nuevo y</t>
         </is>
       </c>
     </row>

--- a/entregables/gestion-proyectos/bases/Base_General.xlsx
+++ b/entregables/gestion-proyectos/bases/Base_General.xlsx
@@ -1572,7 +1572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1865,26 +1865,28 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Acompañamiento a la implementación</t>
+          <t>Cápsulas de refuerzo para supervisores</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Cápsulas</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>105000</v>
+        <v>95000</v>
       </c>
       <c r="F7" s="9" t="inlineStr"/>
       <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="n">
+        <v>80</v>
+      </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr"/>
@@ -1894,20 +1896,40 @@
       <c r="N7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n"/>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="10" t="n"/>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>GEN-001</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Acompañamiento a la implementación</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>105000</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="inlineStr"/>
+      <c r="M8" s="12" t="inlineStr"/>
+      <c r="N8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -2373,16 +2395,32 @@
       <c r="M37" s="11" t="n"/>
       <c r="N37" s="11" t="n"/>
     </row>
+    <row r="38">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Medición objetiva,Tablero BI,Diseño,Cápsulas,Otro"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Baja,Media,Alta"</formula1>
     </dataValidation>
   </dataValidations>

--- a/entregables/gestion-proyectos/bases/Base_General.xlsx
+++ b/entregables/gestion-proyectos/bases/Base_General.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -622,14 +622,14 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Abra la aplicación → barra lateral → Bases y auditoría → «Cargar base de alimentación (Excel)» →</t>
+          <t>La carga la hace un ADMINISTRADOR (CEO, Gerente, Director de Proyectos o Jefe de Operaciones):</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>elija este archivo (también desde la pestaña Guía, botón «Cargar una base ahora»). La carga NO borra lo existente: crea lo nuevo y</t>
+          <t>barra lateral → Bases y auditoría → «Cargar base de alimentación (Excel)» → elija este archivo. La carga NO borra lo existente: crea lo nuevo y</t>
         </is>
       </c>
     </row>
@@ -653,40 +653,47 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>· El cargo responsable de cada producto lo asigna el motor según la categoría (no se escribe en la base):</t>
+          <t>· El cargo responsable lo asigna el motor según la categoría, salvo que la columna «responsable» traiga</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Medición objetiva → Director de Proyectos · Tablero BI → Gestor de Datos 1 · Diseño → Diseñador ·</t>
+          <t xml:space="preserve">  uno de los ocho cargos (sirve, por ejemplo, para elegir entre Gestor de Datos 1 y 2):</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cápsulas → Supervisor Contactabilidad · Otro → coordinación del tipo.</t>
+          <t xml:space="preserve">  Medición objetiva → Director de Proyectos · Tablero BI → Gestor de Datos 1 · Diseño → Diseñador ·</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>· Los usuarios de la aplicación son los ocho cargos: CEO, Gerente, Director de Proyectos, Jefe de Operaciones, Supervisor Contactabilidad, Gestor de Datos 1, Gestor de Datos 2, Diseñador.</t>
+          <t xml:space="preserve">  Cápsulas → Supervisor Contactabilidad · Otro → coordinación del tipo.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>· Empresas, PPR y órdenes que no existan se crean en el catálogo automáticamente.</t>
+          <t>· Los usuarios de la aplicación son los ocho cargos: CEO, Gerente, Director de Proyectos, Jefe de Operaciones, Supervisor Contactabilidad, Gestor de Datos 1, Gestor de Datos 2, Diseñador.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>· Empresas, PPR y órdenes que no existan se crean en el catálogo automáticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>· El seguimiento se registra como novedades en la bitácora del producto, con su tipo y su fecha.</t>
         </is>
@@ -1572,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1589,6 +1596,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1610,6 +1618,7 @@
       <c r="L1" s="5" t="n"/>
       <c r="M1" s="5" t="n"/>
       <c r="N1" s="5" t="n"/>
+      <c r="O1" s="5" t="n"/>
     </row>
     <row r="2" ht="3" customHeight="1">
       <c r="A2" s="6" t="n"/>
@@ -1626,6 +1635,7 @@
       <c r="L2" s="6" t="n"/>
       <c r="M2" s="6" t="n"/>
       <c r="N2" s="6" t="n"/>
+      <c r="O2" s="6" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -1698,6 +1708,11 @@
           <t>notas</t>
         </is>
       </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>responsable</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -1768,6 +1783,11 @@
       <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Opcional.</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>Opcional. Uno de los ocho cargos; si va vacío, asigna el motor.</t>
         </is>
       </c>
     </row>
@@ -1946,6 +1966,7 @@
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n"/>
@@ -1962,6 +1983,7 @@
       <c r="L10" s="10" t="n"/>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -1978,6 +2000,7 @@
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
+      <c r="O11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n"/>
@@ -1994,6 +2017,7 @@
       <c r="L12" s="10" t="n"/>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -2010,6 +2034,7 @@
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
+      <c r="O13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n"/>
@@ -2026,6 +2051,7 @@
       <c r="L14" s="10" t="n"/>
       <c r="M14" s="10" t="n"/>
       <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -2042,6 +2068,7 @@
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
+      <c r="O15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n"/>
@@ -2058,6 +2085,7 @@
       <c r="L16" s="10" t="n"/>
       <c r="M16" s="10" t="n"/>
       <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -2074,6 +2102,7 @@
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="11" t="n"/>
+      <c r="O17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
@@ -2090,6 +2119,7 @@
       <c r="L18" s="10" t="n"/>
       <c r="M18" s="10" t="n"/>
       <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -2106,6 +2136,7 @@
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
+      <c r="O19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n"/>
@@ -2122,6 +2153,7 @@
       <c r="L20" s="10" t="n"/>
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -2138,6 +2170,7 @@
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
+      <c r="O21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n"/>
@@ -2154,6 +2187,7 @@
       <c r="L22" s="10" t="n"/>
       <c r="M22" s="10" t="n"/>
       <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -2170,6 +2204,7 @@
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
+      <c r="O23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -2186,6 +2221,7 @@
       <c r="L24" s="10" t="n"/>
       <c r="M24" s="10" t="n"/>
       <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -2202,6 +2238,7 @@
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
+      <c r="O25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n"/>
@@ -2218,6 +2255,7 @@
       <c r="L26" s="10" t="n"/>
       <c r="M26" s="10" t="n"/>
       <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -2234,6 +2272,7 @@
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
+      <c r="O27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n"/>
@@ -2250,6 +2289,7 @@
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="10" t="n"/>
       <c r="N28" s="10" t="n"/>
+      <c r="O28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -2266,6 +2306,7 @@
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="11" t="n"/>
       <c r="N29" s="11" t="n"/>
+      <c r="O29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n"/>
@@ -2282,6 +2323,7 @@
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="10" t="n"/>
       <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -2298,6 +2340,7 @@
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="11" t="n"/>
       <c r="N31" s="11" t="n"/>
+      <c r="O31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n"/>
@@ -2314,6 +2357,7 @@
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="10" t="n"/>
       <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -2330,6 +2374,7 @@
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="11" t="n"/>
       <c r="N33" s="11" t="n"/>
+      <c r="O33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n"/>
@@ -2346,6 +2391,7 @@
       <c r="L34" s="10" t="n"/>
       <c r="M34" s="10" t="n"/>
       <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -2362,6 +2408,7 @@
       <c r="L35" s="11" t="n"/>
       <c r="M35" s="11" t="n"/>
       <c r="N35" s="11" t="n"/>
+      <c r="O35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n"/>
@@ -2378,6 +2425,7 @@
       <c r="L36" s="10" t="n"/>
       <c r="M36" s="10" t="n"/>
       <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -2394,6 +2442,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="11" t="n"/>
       <c r="N37" s="11" t="n"/>
+      <c r="O37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n"/>
@@ -2410,11 +2459,12 @@
       <c r="L38" s="10" t="n"/>
       <c r="M38" s="10" t="n"/>
       <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C5:C38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/entregables/gestion-proyectos/bases/Base_General.xlsx
+++ b/entregables/gestion-proyectos/bases/Base_General.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B28"/>
+  <dimension ref="B2:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -622,78 +622,85 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>La carga la hace un ADMINISTRADOR (CEO, Gerente, Director de Proyectos o Jefe de Operaciones):</t>
+          <t>La carga la hace un ADMINISTRADOR (por defecto CEO, Gerente, Director de Proyectos y Jefe de</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>barra lateral → Bases y auditoría → «Cargar base de alimentación (Excel)» → elija este archivo. La carga NO borra lo existente: crea lo nuevo y</t>
+          <t>Operaciones; el perfil se asigna en la app: Parametrización → Perfiles y accesos):</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>barra lateral → Bases y auditoría → «Cargar base de alimentación (Excel)» → elija este archivo. La carga NO borra lo existente: crea lo nuevo y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>actualiza lo que coincida por código de proyecto y nombre de producto, y muestra un resumen de lo cargado.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>REGLAS QUE APLICA LA CARGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>· El cargo responsable lo asigna el motor según la categoría, salvo que la columna «responsable» traiga</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  uno de los ocho cargos (sirve, por ejemplo, para elegir entre Gestor de Datos 1 y 2):</t>
+          <t>· El cargo responsable lo asigna el motor según la categoría, salvo que la columna «responsable» traiga</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Medición objetiva → Director de Proyectos · Tablero BI → Gestor de Datos 1 · Diseño → Diseñador ·</t>
+          <t xml:space="preserve">  uno de los ocho cargos (sirve, por ejemplo, para elegir entre Gestor de Datos 1 y 2):</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cápsulas → Supervisor Contactabilidad · Otro → coordinación del tipo.</t>
+          <t xml:space="preserve">  Medición objetiva → Director de Proyectos · Tablero BI → Gestor de Datos 1 · Diseño → Diseñador ·</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>· Los usuarios de la aplicación son los ocho cargos: CEO, Gerente, Director de Proyectos, Jefe de Operaciones, Supervisor Contactabilidad, Gestor de Datos 1, Gestor de Datos 2, Diseñador.</t>
+          <t xml:space="preserve">  Cápsulas → Supervisor Contactabilidad · Otro → coordinación del tipo.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>· Empresas, PPR y órdenes que no existan se crean en el catálogo automáticamente.</t>
+          <t>· Los usuarios de la aplicación son los ocho cargos: CEO, Gerente, Director de Proyectos, Jefe de Operaciones, Supervisor Contactabilidad, Gestor de Datos 1, Gestor de Datos 2, Diseñador.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>· Empresas, PPR y órdenes que no existan se crean en el catálogo automáticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>· El seguimiento se registra como novedades en la bitácora del producto, con su tipo y su fecha.</t>
         </is>
